--- a/BOM/BOM.xlsx
+++ b/BOM/BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BCDACE4C-83B1-4F19-8E61-F96100465B39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ABFEC63-1DF5-4D41-BE96-1080F139D37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="1860" windowWidth="15375" windowHeight="7875" xr2:uid="{4F0AB824-9660-40CF-8AD8-A3265D3FB3E4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{4F0AB824-9660-40CF-8AD8-A3265D3FB3E4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>ID</t>
   </si>
@@ -53,21 +53,6 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>Manufacturer Part</t>
-  </si>
-  <si>
-    <t>Manufacturer</t>
-  </si>
-  <si>
-    <t>Supplier</t>
-  </si>
-  <si>
-    <t>Supplier Part</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
     <t>DC-DC-STEP-DOWN-MP1584</t>
   </si>
   <si>
@@ -83,15 +68,6 @@
     <t>SMD_L10.0-W3.5</t>
   </si>
   <si>
-    <t>null</t>
-  </si>
-  <si>
-    <t>LCSC</t>
-  </si>
-  <si>
-    <t>C9900023671</t>
-  </si>
-  <si>
     <t>1000uF</t>
   </si>
   <si>
@@ -101,15 +77,6 @@
     <t>SARAWUT_C1000UF</t>
   </si>
   <si>
-    <t>KM108M050J25RR0VH2FP0</t>
-  </si>
-  <si>
-    <t>CX(承兴)</t>
-  </si>
-  <si>
-    <t>C18104</t>
-  </si>
-  <si>
     <t>THREE PIN PINHEADER</t>
   </si>
   <si>
@@ -125,12 +92,6 @@
     <t>FIXED RESISTOR</t>
   </si>
   <si>
-    <t>EWWR0001J20R0T9</t>
-  </si>
-  <si>
-    <t>X16151710</t>
-  </si>
-  <si>
     <t>RC522 COPY</t>
   </si>
   <si>
@@ -158,9 +119,6 @@
     <t>LCD_DISPLAY_2X16_I2C</t>
   </si>
   <si>
-    <t>Joy-IT</t>
-  </si>
-  <si>
     <t>JST PH2</t>
   </si>
   <si>
@@ -177,9 +135,6 @@
   </si>
   <si>
     <t>ESP32-C3_SUPERMINI:MODULE_ESP32-C3_SUPERMINI</t>
-  </si>
-  <si>
-    <t>C9900147397</t>
   </si>
 </sst>
 </file>
@@ -551,10 +506,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C688329C-9FC8-476E-8C4A-B02647501062}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -570,258 +531,192 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5">
-        <v>0.23499999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
-      <c r="F7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
-      <c r="H10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="E12">
         <v>1</v>
-      </c>
-      <c r="F12" t="s">
-        <v>44</v>
-      </c>
-      <c r="H12" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
